--- a/documents/development_timeline.xlsx
+++ b/documents/development_timeline.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ba09a449634813ec/Documents/Work_Stuff/LLMs/LARS/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ba09a449634813ec/Documents/Work_Stuff/LLMs/LARS-Enterprise/documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="239" documentId="8_{AB3C9F72-D363-481D-A6D6-DC7960B354FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{512E55D5-F8DF-43BA-A349-C19FC71DA0A3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21840" xr2:uid="{637D5A6A-77E8-4C97-84B4-9D5CE4B2CBCB}"/>
+    <workbookView xWindow="-105" yWindow="165" windowWidth="38610" windowHeight="15885" xr2:uid="{637D5A6A-77E8-4C97-84B4-9D5CE4B2CBCB}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -456,10 +456,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
